--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.58802406364391</v>
+        <v>7.083053910342136</v>
       </c>
       <c r="D2" t="n">
-        <v>43.69144467805706</v>
+        <v>7.099859760184272</v>
       </c>
       <c r="E2" t="n">
-        <v>12.68922325412578</v>
+        <v>2.061998778795439</v>
       </c>
       <c r="F2" t="n">
-        <v>13.70029747233692</v>
+        <v>2.22629833925475</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.85056720117054</v>
+        <v>2.250717170190213</v>
       </c>
       <c r="D3" t="n">
-        <v>12.15610591227297</v>
+        <v>1.975367210744358</v>
       </c>
       <c r="E3" t="n">
-        <v>12.68922325412578</v>
+        <v>2.061998778795439</v>
       </c>
       <c r="F3" t="n">
-        <v>13.70029747233692</v>
+        <v>2.22629833925475</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.03632160016857</v>
+        <v>3.743402260027392</v>
       </c>
       <c r="D4" t="n">
-        <v>20.13010614915859</v>
+        <v>3.271142249238272</v>
       </c>
       <c r="E4" t="n">
-        <v>12.68922325412578</v>
+        <v>2.061998778795439</v>
       </c>
       <c r="F4" t="n">
-        <v>13.70029747233692</v>
+        <v>2.22629833925475</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.33310133651661</v>
+        <v>6.87912896718395</v>
       </c>
       <c r="D5" t="n">
-        <v>42.18054356894057</v>
+        <v>6.854338329952843</v>
       </c>
       <c r="E5" t="n">
-        <v>12.68922325412578</v>
+        <v>2.061998778795439</v>
       </c>
       <c r="F5" t="n">
-        <v>13.70029747233692</v>
+        <v>2.22629833925475</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
